--- a/output/xlsx/AdministradorEditaEcommerce--GT-.xlsx
+++ b/output/xlsx/AdministradorEditaEcommerce--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="53">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 8 test case(s)</t>
+    <t>Size: 5 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -116,7 +116,7 @@
     <t>Administrador: clica no botao de atualizar</t>
   </si>
   <si>
-    <t>SYSTEM notifica usuario de que o Ecommerce foi atualizado com sucesso</t>
+    <t>SYSTEM atualiza os dados do E-commerce no sistema</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -128,7 +128,7 @@
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Ordena lista de Ecommerce</t>
+    <t>Alternative Flow 1: Usuario ordena lista de Ecommerce</t>
   </si>
   <si>
     <t>Administrador: clica em um dos botões de ordenacao associada a uma coluna da tabela</t>
@@ -137,7 +137,7 @@
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Navega por paginas de tabela</t>
+    <t>Alternative Flow 2: Usuario navega por paginas de tabela</t>
   </si>
   <si>
     <t>Administrador: clica em botao de navegacao de paginas de tabela</t>
@@ -146,49 +146,22 @@
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 3: Filtra lista de Ecommerce</t>
-  </si>
-  <si>
-    <t>Administrador: preenche campos de filtragem</t>
+    <t>Exception Flow 1: Nao insere algum dado obrigatório'</t>
+  </si>
+  <si>
+    <t>SYSTEM informa que os dados obrigatórios devem ser preenchidos</t>
+  </si>
+  <si>
+    <t>Administrador: adiciona dados corretos e clica em 'Atualizar</t>
+  </si>
+  <si>
+    <t>SYSTEM processes action successfully</t>
+  </si>
+  <si>
+    <t>Flow interrupted due to exception / error</t>
   </si>
   <si>
     <t>TC5</t>
-  </si>
-  <si>
-    <t>Alternative Flow 4: Cancela atualizacao de Ecommerce</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao Cancelar</t>
-  </si>
-  <si>
-    <t>TC6</t>
-  </si>
-  <si>
-    <t>Alternative Flow 5: Volta para tela inicial de sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao Voltar</t>
-  </si>
-  <si>
-    <t>TC7</t>
-  </si>
-  <si>
-    <t>Exception Flow 1: Nao insere algum dado obrigatório'</t>
-  </si>
-  <si>
-    <t>SYSTEM informa que os dados obrigatórios devem ser preenchidos</t>
-  </si>
-  <si>
-    <t>Administrador: adiciona dados corretos e clica em 'Atualizar</t>
-  </si>
-  <si>
-    <t>SYSTEM processes action successfully</t>
-  </si>
-  <si>
-    <t>Flow interrupted due to exception / error</t>
-  </si>
-  <si>
-    <t>TC8</t>
   </si>
   <si>
     <t>Exception Flow 2: Usuario insere algum dado invalido</t>
@@ -289,13 +262,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="71.015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="59.4140625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="54.4765625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="17.578125" customWidth="true" bestFit="true"/>
   </cols>
@@ -880,13 +853,13 @@
         <v>2.0</v>
       </c>
       <c r="B46" t="s" s="3">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D46" t="s" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s" s="3">
         <v>27</v>
@@ -900,13 +873,13 @@
         <v>3.0</v>
       </c>
       <c r="B47" t="s" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D47" t="s" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E47" t="s" s="3">
         <v>27</v>
@@ -920,13 +893,13 @@
         <v>4.0</v>
       </c>
       <c r="B48" t="s" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D48" t="s" s="3">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s" s="3">
         <v>27</v>
@@ -940,13 +913,13 @@
         <v>5.0</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D49" t="s" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E49" t="s" s="3">
         <v>27</v>
@@ -960,7 +933,7 @@
         <v>35</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53">
@@ -968,7 +941,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s" s="1">
         <v>13</v>
@@ -982,7 +955,7 @@
         <v>15</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E54" t="s" s="1">
         <v>17</v>
@@ -1041,13 +1014,13 @@
         <v>2.0</v>
       </c>
       <c r="B58" t="s" s="3">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D58" t="s" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E58" t="s" s="3">
         <v>27</v>
@@ -1061,13 +1034,13 @@
         <v>3.0</v>
       </c>
       <c r="B59" t="s" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D59" t="s" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E59" t="s" s="3">
         <v>27</v>
@@ -1081,13 +1054,13 @@
         <v>4.0</v>
       </c>
       <c r="B60" t="s" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D60" t="s" s="3">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E60" t="s" s="3">
         <v>27</v>
@@ -1101,13 +1074,13 @@
         <v>5.0</v>
       </c>
       <c r="B61" t="s" s="3">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C61" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>27</v>
@@ -1121,530 +1094,7 @@
         <v>35</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="C65" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E65" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="E66" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D68" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F68" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B69" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C69" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D69" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E69" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F69" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B70" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C70" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D70" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E70" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F70" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B71" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C71" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D71" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E71" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F71" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B72" t="s" s="3">
-        <v>51</v>
-      </c>
-      <c r="C72" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D72" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E72" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F72" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B73" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C73" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D73" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E73" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F73" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B74" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C74" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D74" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E74" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F74" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B75" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C75" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D75" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E75" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F75" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="C79" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E79" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="E80" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B81" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E82" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F82" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B83" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C83" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D83" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E83" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F83" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B84" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C84" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D84" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E84" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F84" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B85" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C85" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D85" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E85" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F85" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B86" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C86" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D86" t="s" s="3">
-        <v>54</v>
-      </c>
-      <c r="E86" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F86" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B87" t="s" s="3">
-        <v>55</v>
-      </c>
-      <c r="C87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D87" t="s" s="3">
-        <v>56</v>
-      </c>
-      <c r="E87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F87" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B88" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="C91" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E91" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="E92" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B93" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F94" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B95" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C95" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D95" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E95" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F95" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B96" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C96" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D96" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E96" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F96" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B97" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C97" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D97" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E97" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F97" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B98" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C98" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D98" t="s" s="3">
-        <v>60</v>
-      </c>
-      <c r="E98" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F98" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B99" t="s" s="3">
-        <v>61</v>
-      </c>
-      <c r="C99" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D99" t="s" s="3">
-        <v>56</v>
-      </c>
-      <c r="E99" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F99" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B100" t="s" s="0">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
